--- a/artfynd/A 27286-2025 artfynd.xlsx
+++ b/artfynd/A 27286-2025 artfynd.xlsx
@@ -873,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126448678</v>
+        <v>126522515</v>
       </c>
       <c r="B4" t="n">
-        <v>101447</v>
+        <v>95857</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -884,21 +884,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221235</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>630524</v>
+        <v>630602</v>
       </c>
       <c r="R4" t="n">
-        <v>6665565</v>
+        <v>6665591</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -938,12 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -970,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126522515</v>
+        <v>126448678</v>
       </c>
       <c r="B5" t="n">
-        <v>95857</v>
+        <v>101447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>221235</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630602</v>
+        <v>630524</v>
       </c>
       <c r="R5" t="n">
-        <v>6665591</v>
+        <v>6665565</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1463,10 +1463,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126448715</v>
+        <v>126448688</v>
       </c>
       <c r="B10" t="n">
-        <v>105396</v>
+        <v>95714</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1474,21 +1474,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>2818</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630528</v>
+        <v>630533</v>
       </c>
       <c r="R10" t="n">
-        <v>6665570</v>
+        <v>6665573</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1560,10 +1560,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126448688</v>
+        <v>126448677</v>
       </c>
       <c r="B11" t="n">
-        <v>95714</v>
+        <v>101447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1571,34 +1571,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2818</v>
+        <v>221235</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630533</v>
+        <v>630534</v>
       </c>
       <c r="R11" t="n">
-        <v>6665573</v>
+        <v>6665553</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1639,6 +1643,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1657,10 +1662,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126448677</v>
+        <v>126448715</v>
       </c>
       <c r="B12" t="n">
-        <v>101447</v>
+        <v>105396</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1668,38 +1673,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221235</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630534</v>
+        <v>630528</v>
       </c>
       <c r="R12" t="n">
-        <v>6665553</v>
+        <v>6665570</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1740,7 +1741,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1856,10 +1856,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126448713</v>
+        <v>126448676</v>
       </c>
       <c r="B14" t="n">
-        <v>58027</v>
+        <v>101447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1867,34 +1867,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>221235</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630503</v>
+        <v>630530</v>
       </c>
       <c r="R14" t="n">
-        <v>6665527</v>
+        <v>6665571</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1935,6 +1939,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1953,10 +1958,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126448676</v>
+        <v>126448713</v>
       </c>
       <c r="B15" t="n">
-        <v>101447</v>
+        <v>58027</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1964,38 +1969,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221235</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630530</v>
+        <v>630503</v>
       </c>
       <c r="R15" t="n">
-        <v>6665571</v>
+        <v>6665527</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2036,7 +2037,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2180,7 +2180,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126448705</v>
+        <v>126522501</v>
       </c>
       <c r="B17" t="n">
         <v>98395</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630589</v>
+        <v>630612</v>
       </c>
       <c r="R17" t="n">
-        <v>6665505</v>
+        <v>6665502</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2245,12 +2245,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2277,7 +2277,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126522501</v>
+        <v>126448705</v>
       </c>
       <c r="B18" t="n">
         <v>98395</v>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630612</v>
+        <v>630589</v>
       </c>
       <c r="R18" t="n">
-        <v>6665502</v>
+        <v>6665505</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2342,12 +2342,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2471,7 +2471,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126448723</v>
+        <v>126448722</v>
       </c>
       <c r="B20" t="n">
         <v>100543</v>
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630513</v>
+        <v>630510</v>
       </c>
       <c r="R20" t="n">
-        <v>6665593</v>
+        <v>6665590</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2568,7 +2568,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126448722</v>
+        <v>126448723</v>
       </c>
       <c r="B21" t="n">
         <v>100543</v>
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630510</v>
+        <v>630513</v>
       </c>
       <c r="R21" t="n">
-        <v>6665590</v>
+        <v>6665593</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>

--- a/artfynd/A 27286-2025 artfynd.xlsx
+++ b/artfynd/A 27286-2025 artfynd.xlsx
@@ -1366,10 +1366,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126448716</v>
+        <v>126448688</v>
       </c>
       <c r="B9" t="n">
-        <v>95810</v>
+        <v>95714</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1377,21 +1377,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630529</v>
+        <v>630533</v>
       </c>
       <c r="R9" t="n">
-        <v>6665579</v>
+        <v>6665573</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1463,10 +1463,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126448688</v>
+        <v>126448716</v>
       </c>
       <c r="B10" t="n">
-        <v>95714</v>
+        <v>95810</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1474,21 +1474,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630533</v>
+        <v>630529</v>
       </c>
       <c r="R10" t="n">
-        <v>6665573</v>
+        <v>6665579</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -2180,7 +2180,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126522501</v>
+        <v>126448705</v>
       </c>
       <c r="B17" t="n">
         <v>98395</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630612</v>
+        <v>630589</v>
       </c>
       <c r="R17" t="n">
-        <v>6665502</v>
+        <v>6665505</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2245,12 +2245,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2277,7 +2277,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126448705</v>
+        <v>126522501</v>
       </c>
       <c r="B18" t="n">
         <v>98395</v>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630589</v>
+        <v>630612</v>
       </c>
       <c r="R18" t="n">
-        <v>6665505</v>
+        <v>6665502</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2342,12 +2342,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 27286-2025 artfynd.xlsx
+++ b/artfynd/A 27286-2025 artfynd.xlsx
@@ -1366,10 +1366,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126448688</v>
+        <v>126448716</v>
       </c>
       <c r="B9" t="n">
-        <v>95714</v>
+        <v>95810</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1377,21 +1377,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630533</v>
+        <v>630529</v>
       </c>
       <c r="R9" t="n">
-        <v>6665573</v>
+        <v>6665579</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1463,10 +1463,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126448716</v>
+        <v>126448688</v>
       </c>
       <c r="B10" t="n">
-        <v>95810</v>
+        <v>95714</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1474,21 +1474,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630529</v>
+        <v>630533</v>
       </c>
       <c r="R10" t="n">
-        <v>6665579</v>
+        <v>6665573</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -2180,7 +2180,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126448705</v>
+        <v>126522501</v>
       </c>
       <c r="B17" t="n">
         <v>98395</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630589</v>
+        <v>630612</v>
       </c>
       <c r="R17" t="n">
-        <v>6665505</v>
+        <v>6665502</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2245,12 +2245,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2277,7 +2277,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126522501</v>
+        <v>126448705</v>
       </c>
       <c r="B18" t="n">
         <v>98395</v>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630612</v>
+        <v>630589</v>
       </c>
       <c r="R18" t="n">
-        <v>6665502</v>
+        <v>6665505</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2342,12 +2342,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 27286-2025 artfynd.xlsx
+++ b/artfynd/A 27286-2025 artfynd.xlsx
@@ -2668,7 +2668,7 @@
         <v>127021127</v>
       </c>
       <c r="B22" t="n">
-        <v>100450</v>
+        <v>100525</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>127021144</v>
       </c>
       <c r="B23" t="n">
-        <v>95857</v>
+        <v>95932</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>127021124</v>
       </c>
       <c r="B24" t="n">
-        <v>96614</v>
+        <v>96689</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>127021121</v>
       </c>
       <c r="B25" t="n">
-        <v>101447</v>
+        <v>101522</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27286-2025 artfynd.xlsx
+++ b/artfynd/A 27286-2025 artfynd.xlsx
@@ -2668,7 +2668,7 @@
         <v>127021127</v>
       </c>
       <c r="B22" t="n">
-        <v>100525</v>
+        <v>100531</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>127021144</v>
       </c>
       <c r="B23" t="n">
-        <v>95932</v>
+        <v>95938</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>127021124</v>
       </c>
       <c r="B24" t="n">
-        <v>96689</v>
+        <v>96695</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>127021121</v>
       </c>
       <c r="B25" t="n">
-        <v>101522</v>
+        <v>101528</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27286-2025 artfynd.xlsx
+++ b/artfynd/A 27286-2025 artfynd.xlsx
@@ -2668,7 +2668,7 @@
         <v>127021127</v>
       </c>
       <c r="B22" t="n">
-        <v>100531</v>
+        <v>100532</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>127021144</v>
       </c>
       <c r="B23" t="n">
-        <v>95938</v>
+        <v>95939</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>127021124</v>
       </c>
       <c r="B24" t="n">
-        <v>96695</v>
+        <v>96696</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>127021121</v>
       </c>
       <c r="B25" t="n">
-        <v>101528</v>
+        <v>101529</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27286-2025 artfynd.xlsx
+++ b/artfynd/A 27286-2025 artfynd.xlsx
@@ -2668,7 +2668,7 @@
         <v>127021127</v>
       </c>
       <c r="B22" t="n">
-        <v>100532</v>
+        <v>100536</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>127021144</v>
       </c>
       <c r="B23" t="n">
-        <v>95939</v>
+        <v>95943</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>127021124</v>
       </c>
       <c r="B24" t="n">
-        <v>96696</v>
+        <v>96700</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>127021121</v>
       </c>
       <c r="B25" t="n">
-        <v>101529</v>
+        <v>101533</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27286-2025 artfynd.xlsx
+++ b/artfynd/A 27286-2025 artfynd.xlsx
@@ -2668,7 +2668,7 @@
         <v>127021127</v>
       </c>
       <c r="B22" t="n">
-        <v>100536</v>
+        <v>100537</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>127021121</v>
       </c>
       <c r="B25" t="n">
-        <v>101533</v>
+        <v>101534</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27286-2025 artfynd.xlsx
+++ b/artfynd/A 27286-2025 artfynd.xlsx
@@ -2668,7 +2668,7 @@
         <v>127021127</v>
       </c>
       <c r="B22" t="n">
-        <v>100537</v>
+        <v>100539</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>127021144</v>
       </c>
       <c r="B23" t="n">
-        <v>95943</v>
+        <v>95945</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>127021124</v>
       </c>
       <c r="B24" t="n">
-        <v>96700</v>
+        <v>96702</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>127021121</v>
       </c>
       <c r="B25" t="n">
-        <v>101534</v>
+        <v>101536</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27286-2025 artfynd.xlsx
+++ b/artfynd/A 27286-2025 artfynd.xlsx
@@ -2668,7 +2668,7 @@
         <v>127021127</v>
       </c>
       <c r="B22" t="n">
-        <v>100539</v>
+        <v>100545</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>127021144</v>
       </c>
       <c r="B23" t="n">
-        <v>95945</v>
+        <v>95951</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>127021124</v>
       </c>
       <c r="B24" t="n">
-        <v>96702</v>
+        <v>96708</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>127021121</v>
       </c>
       <c r="B25" t="n">
-        <v>101536</v>
+        <v>101542</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27286-2025 artfynd.xlsx
+++ b/artfynd/A 27286-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3057,6 +3057,103 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128493968</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101657</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>630542</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6665526</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27286-2025 artfynd.xlsx
+++ b/artfynd/A 27286-2025 artfynd.xlsx
@@ -3062,7 +3062,7 @@
         <v>128493968</v>
       </c>
       <c r="B26" t="n">
-        <v>101657</v>
+        <v>101665</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 27286-2025 artfynd.xlsx
+++ b/artfynd/A 27286-2025 artfynd.xlsx
@@ -3062,7 +3062,7 @@
         <v>128493968</v>
       </c>
       <c r="B26" t="n">
-        <v>101665</v>
+        <v>101673</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
